--- a/data/processed/positivacao/2025-12_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-12_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27441,7 +27441,7 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr"/>
@@ -38715,7 +38715,7 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr"/>
@@ -66957,7 +66957,7 @@
     <row r="2564">
       <c r="A2564" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2564" t="inlineStr"/>
@@ -68576,12 +68576,12 @@
       <c r="A2627" t="inlineStr"/>
       <c r="B2627" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 13 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 16.399,15
+          <t>Vendedor 1 - VENDEDOR 01: positivou 13 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 16.399,15
 Vendedor 18 - LOJA: positivou 329 cliente(s), não positivou 608 cliente(s) - Total vendido: R$ 116.350,33
-Vendedor 3 - FERNANDA: positivou 128 cliente(s), não positivou 305 cliente(s) - Total vendido: R$ 162.379,36
-Vendedor 4 - DANIELA: positivou 131 cliente(s), não positivou 510 cliente(s) - Total vendido: R$ 88.349,54
+Vendedor 3 - VENDEDOR 03: positivou 128 cliente(s), não positivou 305 cliente(s) - Total vendido: R$ 162.379,36
+Vendedor 4 - VENDEDOR 04: positivou 131 cliente(s), não positivou 510 cliente(s) - Total vendido: R$ 88.349,54
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 444 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 1 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 1 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2627" t="inlineStr"/>
